--- a/templates/1_ThietBi.xlsx
+++ b/templates/1_ThietBi.xlsx
@@ -694,7 +694,6 @@
           <t>24 tháng</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Máy chiếu</t>
@@ -711,7 +710,6 @@
           <t>Nhóm Công Nghệ Thông Tin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
